--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1551,6 +1551,116 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133757442</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102253</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>625892</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6722513</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Inger Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>133757442</v>
       </c>
       <c r="B9" t="n">
-        <v>102253</v>
+        <v>102255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>133757442</v>
       </c>
       <c r="B9" t="n">
-        <v>102255</v>
+        <v>102261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>133757442</v>
       </c>
       <c r="B9" t="n">
-        <v>102261</v>
+        <v>102263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>133757442</v>
       </c>
       <c r="B9" t="n">
-        <v>102263</v>
+        <v>102291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>133757442</v>
       </c>
       <c r="B9" t="n">
-        <v>102291</v>
+        <v>102301</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>133757442</v>
       </c>
       <c r="B9" t="n">
-        <v>102301</v>
+        <v>102303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>133757442</v>
       </c>
       <c r="B9" t="n">
-        <v>102304</v>
+        <v>102311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3719875</v>
+        <v>72215059</v>
       </c>
       <c r="B2" t="n">
-        <v>103163</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,62 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221137</v>
+        <v>100399</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Turkos blåvinge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Aricia nicias</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Meigen, 1829)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SSO Grinduga, 480 m NV-NNV Hobäcktjärnens N-spets (fjärilsvägen), Gstr</t>
+          <t>Fjärilsvägen Grinduga, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625882.8000412157</v>
+        <v>625921</v>
       </c>
       <c r="R2" t="n">
-        <v>6722451.776284857</v>
+        <v>6722391</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +765,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-05-31</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-05-31</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vägren + vägdike.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,81 +789,92 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägren, vägdike</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Per-Olof Bengtsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Per-Olof Bengtsson, Anita Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17089909</v>
+        <v>72214967</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>101688</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kattunvisslare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrgus alveus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hübner, 1803)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fjärilsvägen SSO Grinduga, 500 m NNV Hobäcktjärnens N-ände, Gstr</t>
+          <t>Fjärilsvägen Grinduga, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625878.0504344931</v>
+        <v>625921</v>
       </c>
       <c r="R3" t="n">
-        <v>6722460.944415514</v>
+        <v>6722391</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +898,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-07-18</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,81 +922,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsbilvägren</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Per-Olof Bengtsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Per-Olof Bengtsson, Anita Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17110010</v>
+        <v>126617320</v>
       </c>
       <c r="B4" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221137</v>
+        <v>102918</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Citronfläckad kärrtrollslända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Leucorrhinia pectoralis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Charpentier, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fjärilsvägen, Grinduga, Gstr</t>
+          <t>Fjärilsvägen, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625880.7654317224</v>
+        <v>625906</v>
       </c>
       <c r="R4" t="n">
-        <v>6722453.670204137</v>
+        <v>6722531</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,22 +1015,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-06-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,78 +1029,69 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Owe Rosengren</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Owe Rosengren, Johan Södercrantz</t>
+          <t>Linnea Helmersson, Sofia Lundell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72215059</v>
+        <v>72315952</v>
       </c>
       <c r="B5" t="n">
-        <v>42566</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100399</v>
+        <v>201028</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Turkos blåvinge</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aricia nicias</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Meigen, 1829)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>friflygande</t>
@@ -1120,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625921.3340426222</v>
+        <v>625921</v>
       </c>
       <c r="R5" t="n">
-        <v>6722391.222976416</v>
+        <v>6722391</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1165,7 +1153,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,15 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72214967</v>
+        <v>72253244</v>
       </c>
       <c r="B6" t="n">
-        <v>42524</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,26 +1192,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101688</v>
+        <v>201075</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattunvisslare</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrgus alveus</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hübner, 1803)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1258,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625921.3340426222</v>
+        <v>625921</v>
       </c>
       <c r="R6" t="n">
-        <v>6722391.222976416</v>
+        <v>6722391</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1324,55 +1307,80 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per-Olof Bengtsson, Anita Persson</t>
+          <t>Anita Persson, Per-Olof Bengtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97414932</v>
+        <v>72214998</v>
       </c>
       <c r="B7" t="n">
-        <v>105634</v>
+        <v>43258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>201129</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älgängsån, 100 m S bron, vägens östra sida, kontr majvivelok, Gstr</t>
+          <t>Fjärilsvägen Grinduga, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625879</v>
+        <v>625921</v>
       </c>
       <c r="R7" t="n">
-        <v>6722462</v>
+        <v>6722391</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1396,12 +1404,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2006-06-04</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2006-06-04</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,80 +1428,92 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kulturmark, vägdike</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 291885H</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Per-Olof Bengtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Åke Lundblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Per-Olof Bengtsson, Anita Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97414939</v>
+        <v>72315920</v>
       </c>
       <c r="B8" t="n">
-        <v>105620</v>
+        <v>43285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221137</v>
+        <v>201143</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älgängsån, 100 m S bron, vägens östra sida, kontr majvivelok, Gstr</t>
+          <t>Fjärilsvägen Grinduga, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625879</v>
+        <v>625921</v>
       </c>
       <c r="R8" t="n">
-        <v>6722462</v>
+        <v>6722391</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,12 +1537,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2006-06-04</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2006-06-04</t>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,89 +1561,64 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kulturmark, vägdike</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 291880H</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Per-Olof Bengtsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Åke Lundblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Per-Olof Bengtsson, Anita Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133757442</v>
+        <v>127318913</v>
       </c>
       <c r="B9" t="n">
-        <v>102311</v>
+        <v>43285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>201143</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fjärilsvägen, Gstr</t>
+          <t>Fjärilsvägen, Gävle, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625892</v>
+        <v>625871</v>
       </c>
       <c r="R9" t="n">
-        <v>6722513</v>
+        <v>6722434</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,12 +1645,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,22 +1659,1384 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>72315915</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen Grinduga, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>625921</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6722391</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per-Olof Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per-Olof Bengtsson, Anita Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>17089909</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen SSO Grinduga, 500 m NNV Hobäcktjärnens N-ände, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>625878</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6722461</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2014-07-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2014-07-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsbilvägren</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3689470</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Älgängsån 100 m S bron, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>625873</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6722456</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Årets växt 2006</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>dikesslänt</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3719875</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SSO Grinduga, 480 m NV-NNV Hobäcktjärnens N-spets (fjärilsvägen), Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>625883</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6722452</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2009-05-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2009-05-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Vägren + vägdike.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Vägren, vägdike</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3735108</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>grinduga, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>625877</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6722471</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2012-05-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2012-05-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>vägdike</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15950264</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grinduga, 650 m NNV Hobäcktj., Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>625874</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6722486</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2014-06-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2014-06-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Många i vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Rahm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Rahm, Lars Eric Rahm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17110010</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen, Grinduga, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>625881</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6722454</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2005-06-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2005-06-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Owe Rosengren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Owe Rosengren, Johan Södercrantz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>91458529</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Älgängsån, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>625876</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6722458</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2003-06-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2003-06-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>följearter ej not.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kulturmark, vägdike till skogsväg</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 260185H</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>97414939</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Älgängsån, 100 m S bron, vägens östra sida, kontr majvivelok, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>625879</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6722462</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kulturmark, vägdike</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 291880H</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Åke Lundblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>94019261</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Älgängsån, 100 m S bro, vägens östsida, kontr.majvlok 7, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>625873</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6722456</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>vägens östra sida, 1 ex majviva på vägens V-sida, mycket med gräsdär. Majvivorna i knopp i djupaste delen av diket, resten i perfekt blomning.Mycket med bladrosetter, blommar senare? Där gräset börjar att dominera tar majvivorna slut. En del mossa i botten</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kulturmark, skogsvägren, slänt och dike, kalkpåverkat</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 286337H</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>97414932</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Älgängsån, 100 m S bron, vägens östra sida, kontr majvivelok, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625879</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6722462</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kulturmark, vägdike</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 291885H</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Åke Lundblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133757442</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102318</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>625892</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6722513</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Inger Carlsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Inger Carlsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54803-2025 artfynd.xlsx
+++ b/artfynd/A 54803-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72215059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -938,6 +948,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72214967</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126617320</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1178,6 +1198,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72315952</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1311,6 +1336,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72253244</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1444,6 +1474,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72214998</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1577,6 +1612,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72315920</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1674,6 +1714,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127318913</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1807,6 +1852,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72315915</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1914,6 +1964,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17089909</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2025,6 +2080,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3689470</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2146,6 +2206,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3719875</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2257,6 +2322,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3735108</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2366,6 +2436,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15950264</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2473,6 +2548,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110010</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2589,6 +2669,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91458529</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2700,6 +2785,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97414939</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2816,6 +2906,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94019261</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2927,6 +3022,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97414932</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3037,8 +3137,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133757442</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>